--- a/medical_data/boundary_ablation/results/drive/drive_boundary_ablation.xlsx
+++ b/medical_data/boundary_ablation/results/drive/drive_boundary_ablation.xlsx
@@ -463,16 +463,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6107</v>
+        <v>0.6695</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7632</v>
+        <v>0.7291</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9272</v>
+        <v>0.9556</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9358</v>
+        <v>0.9446</v>
       </c>
     </row>
     <row r="3">
@@ -482,16 +482,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5967</v>
+        <v>0.6622</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8299</v>
+        <v>0.7962</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9059</v>
+        <v>0.9398</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9451000000000001</v>
+        <v>0.9514</v>
       </c>
     </row>
     <row r="4">
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5304</v>
+        <v>0.6683</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7613</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8903</v>
+        <v>0.947</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9081</v>
+        <v>0.9518</v>
       </c>
     </row>
     <row r="5">
@@ -520,16 +520,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.541</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8557</v>
+        <v>0.7825</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8707</v>
+        <v>0.9424</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9348</v>
+        <v>0.9515</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6469</v>
+        <v>0.6704</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7467</v>
+        <v>0.7931</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9445</v>
+        <v>0.9433</v>
       </c>
       <c r="E6" t="n">
-        <v>0.946</v>
+        <v>0.9545</v>
       </c>
     </row>
   </sheetData>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D151"/>
+  <dimension ref="A1:D281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
         <v>1.469924</v>
       </c>
       <c r="D2" t="n">
-        <v>0.318263</v>
+        <v>0.31821</v>
       </c>
     </row>
     <row r="3">
@@ -613,10 +613,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1.365269</v>
+        <v>1.365209</v>
       </c>
       <c r="D3" t="n">
-        <v>0.221608</v>
+        <v>0.221678</v>
       </c>
     </row>
     <row r="4">
@@ -629,10 +629,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1.301899</v>
+        <v>1.301641</v>
       </c>
       <c r="D4" t="n">
-        <v>0.27026</v>
+        <v>0.270833</v>
       </c>
     </row>
     <row r="5">
@@ -645,10 +645,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>1.255198</v>
+        <v>1.254535</v>
       </c>
       <c r="D5" t="n">
-        <v>0.368386</v>
+        <v>0.369679</v>
       </c>
     </row>
     <row r="6">
@@ -661,10 +661,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1.222194</v>
+        <v>1.22086</v>
       </c>
       <c r="D6" t="n">
-        <v>0.450217</v>
+        <v>0.452209</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>1.194168</v>
+        <v>1.191992</v>
       </c>
       <c r="D7" t="n">
-        <v>0.511083</v>
+        <v>0.514023</v>
       </c>
     </row>
     <row r="8">
@@ -693,10 +693,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>1.171736</v>
+        <v>1.168287</v>
       </c>
       <c r="D8" t="n">
-        <v>0.547914</v>
+        <v>0.551148</v>
       </c>
     </row>
     <row r="9">
@@ -709,10 +709,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>1.146334</v>
+        <v>1.141011</v>
       </c>
       <c r="D9" t="n">
-        <v>0.575424</v>
+        <v>0.579922</v>
       </c>
     </row>
     <row r="10">
@@ -725,10 +725,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>1.125596</v>
+        <v>1.118652</v>
       </c>
       <c r="D10" t="n">
-        <v>0.58896</v>
+        <v>0.594102</v>
       </c>
     </row>
     <row r="11">
@@ -741,10 +741,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>1.115253</v>
+        <v>1.107522</v>
       </c>
       <c r="D11" t="n">
-        <v>0.595823</v>
+        <v>0.600396</v>
       </c>
     </row>
     <row r="12">
@@ -757,10 +757,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>1.098647</v>
+        <v>1.08841</v>
       </c>
       <c r="D12" t="n">
-        <v>0.597305</v>
+        <v>0.604028</v>
       </c>
     </row>
     <row r="13">
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>1.084433</v>
+        <v>1.071074</v>
       </c>
       <c r="D13" t="n">
-        <v>0.598132</v>
+        <v>0.60633</v>
       </c>
     </row>
     <row r="14">
@@ -789,10 +789,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>1.074789</v>
+        <v>1.058809</v>
       </c>
       <c r="D14" t="n">
-        <v>0.598554</v>
+        <v>0.609912</v>
       </c>
     </row>
     <row r="15">
@@ -805,10 +805,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>1.066323</v>
+        <v>1.046559</v>
       </c>
       <c r="D15" t="n">
-        <v>0.599742</v>
+        <v>0.6134770000000001</v>
       </c>
     </row>
     <row r="16">
@@ -821,10 +821,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>1.055233</v>
+        <v>1.031815</v>
       </c>
       <c r="D16" t="n">
-        <v>0.597982</v>
+        <v>0.609444</v>
       </c>
     </row>
     <row r="17">
@@ -837,10 +837,10 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>1.051171</v>
+        <v>1.024909</v>
       </c>
       <c r="D17" t="n">
-        <v>0.594496</v>
+        <v>0.613893</v>
       </c>
     </row>
     <row r="18">
@@ -853,10 +853,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>1.042262</v>
+        <v>1.011904</v>
       </c>
       <c r="D18" t="n">
-        <v>0.600321</v>
+        <v>0.627266</v>
       </c>
     </row>
     <row r="19">
@@ -869,10 +869,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>1.034811</v>
+        <v>0.999796</v>
       </c>
       <c r="D19" t="n">
-        <v>0.60637</v>
+        <v>0.630878</v>
       </c>
     </row>
     <row r="20">
@@ -885,10 +885,10 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>1.030655</v>
+        <v>0.991227</v>
       </c>
       <c r="D20" t="n">
-        <v>0.610074</v>
+        <v>0.630958</v>
       </c>
     </row>
     <row r="21">
@@ -901,10 +901,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>1.028417</v>
+        <v>0.984193</v>
       </c>
       <c r="D21" t="n">
-        <v>0.610094</v>
+        <v>0.629651</v>
       </c>
     </row>
     <row r="22">
@@ -917,10 +917,10 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>1.022181</v>
+        <v>0.97283</v>
       </c>
       <c r="D22" t="n">
-        <v>0.610687</v>
+        <v>0.636749</v>
       </c>
     </row>
     <row r="23">
@@ -933,10 +933,10 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>1.020803</v>
+        <v>0.96744</v>
       </c>
       <c r="D23" t="n">
-        <v>0.60989</v>
+        <v>0.639104</v>
       </c>
     </row>
     <row r="24">
@@ -949,10 +949,10 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>1.01654</v>
+        <v>0.957892</v>
       </c>
       <c r="D24" t="n">
-        <v>0.609273</v>
+        <v>0.638415</v>
       </c>
     </row>
     <row r="25">
@@ -965,10 +965,10 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>1.017026</v>
+        <v>0.952569</v>
       </c>
       <c r="D25" t="n">
-        <v>0.608668</v>
+        <v>0.640497</v>
       </c>
     </row>
     <row r="26">
@@ -981,10 +981,10 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>1.01443</v>
+        <v>0.9449379999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6088750000000001</v>
+        <v>0.642363</v>
       </c>
     </row>
     <row r="27">
@@ -997,10 +997,10 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>1.014914</v>
+        <v>0.939667</v>
       </c>
       <c r="D27" t="n">
-        <v>0.609707</v>
+        <v>0.642161</v>
       </c>
     </row>
     <row r="28">
@@ -1013,10 +1013,10 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>1.013136</v>
+        <v>0.934273</v>
       </c>
       <c r="D28" t="n">
-        <v>0.610063</v>
+        <v>0.6402099999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1029,10 +1029,10 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>1.018025</v>
+        <v>0.934992</v>
       </c>
       <c r="D29" t="n">
-        <v>0.609471</v>
+        <v>0.647073</v>
       </c>
     </row>
     <row r="30">
@@ -1045,10 +1045,10 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>1.015986</v>
+        <v>0.927705</v>
       </c>
       <c r="D30" t="n">
-        <v>0.608986</v>
+        <v>0.654721</v>
       </c>
     </row>
     <row r="31">
@@ -1061,1930 +1061,4010 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>1.012699</v>
+        <v>0.919775</v>
       </c>
       <c r="D31" t="n">
-        <v>0.609789</v>
+        <v>0.661595</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>1.495155</v>
+        <v>0.915573</v>
       </c>
       <c r="D32" t="n">
-        <v>0.165647</v>
+        <v>0.662279</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>1.360878</v>
+        <v>0.913478</v>
       </c>
       <c r="D33" t="n">
-        <v>0.224009</v>
+        <v>0.6636570000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>1.291763</v>
+        <v>0.905969</v>
       </c>
       <c r="D34" t="n">
-        <v>0.300008</v>
+        <v>0.66384</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>1.243257</v>
+        <v>0.901774</v>
       </c>
       <c r="D35" t="n">
-        <v>0.51322</v>
+        <v>0.666093</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>1.205521</v>
+        <v>0.8969200000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.563577</v>
+        <v>0.667055</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>1.181589</v>
+        <v>0.896278</v>
       </c>
       <c r="D37" t="n">
-        <v>0.577175</v>
+        <v>0.667093</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>1.155841</v>
+        <v>0.887776</v>
       </c>
       <c r="D38" t="n">
-        <v>0.580593</v>
+        <v>0.666883</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>1.135433</v>
+        <v>0.88995</v>
       </c>
       <c r="D39" t="n">
-        <v>0.583415</v>
+        <v>0.666692</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>1.119126</v>
+        <v>0.884584</v>
       </c>
       <c r="D40" t="n">
-        <v>0.588709</v>
+        <v>0.665613</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>1.107208</v>
+        <v>0.882216</v>
       </c>
       <c r="D41" t="n">
-        <v>0.594821</v>
+        <v>0.666479</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>1.096001</v>
+        <v>0.880543</v>
       </c>
       <c r="D42" t="n">
-        <v>0.593058</v>
+        <v>0.666489</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>1.08257</v>
+        <v>0.873966</v>
       </c>
       <c r="D43" t="n">
-        <v>0.5858</v>
+        <v>0.663872</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>1.070941</v>
+        <v>0.876295</v>
       </c>
       <c r="D44" t="n">
-        <v>0.581853</v>
+        <v>0.663373</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>1.0626</v>
+        <v>0.871599</v>
       </c>
       <c r="D45" t="n">
-        <v>0.580837</v>
+        <v>0.663236</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>1.052906</v>
+        <v>0.8670369999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.583352</v>
+        <v>0.663395</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>1.049127</v>
+        <v>0.866072</v>
       </c>
       <c r="D47" t="n">
-        <v>0.585618</v>
+        <v>0.664761</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>1.042753</v>
+        <v>0.867065</v>
       </c>
       <c r="D48" t="n">
-        <v>0.5895550000000001</v>
+        <v>0.666578</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>1.039244</v>
+        <v>0.86437</v>
       </c>
       <c r="D49" t="n">
-        <v>0.594368</v>
+        <v>0.668745</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>1.035179</v>
+        <v>0.861228</v>
       </c>
       <c r="D50" t="n">
-        <v>0.596692</v>
+        <v>0.6694830000000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>1.027372</v>
+        <v>0.86266</v>
       </c>
       <c r="D51" t="n">
-        <v>0.596343</v>
+        <v>0.668358</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>1.029362</v>
+        <v>0.855422</v>
       </c>
       <c r="D52" t="n">
-        <v>0.594536</v>
+        <v>0.6670430000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>1.024608</v>
+        <v>0.862044</v>
       </c>
       <c r="D53" t="n">
-        <v>0.594399</v>
+        <v>0.664714</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>1.022058</v>
+        <v>0.859779</v>
       </c>
       <c r="D54" t="n">
-        <v>0.592433</v>
+        <v>0.664511</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>1.025589</v>
+        <v>0.858572</v>
       </c>
       <c r="D55" t="n">
-        <v>0.592179</v>
+        <v>0.665717</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>1.020691</v>
+        <v>0.852823</v>
       </c>
       <c r="D56" t="n">
-        <v>0.592457</v>
+        <v>0.666463</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>1.021847</v>
+        <v>0.856931</v>
       </c>
       <c r="D57" t="n">
-        <v>0.593269</v>
+        <v>0.666183</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>1.017529</v>
+        <v>0.853288</v>
       </c>
       <c r="D58" t="n">
-        <v>0.593561</v>
+        <v>0.666936</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>1.022752</v>
+        <v>0.852608</v>
       </c>
       <c r="D59" t="n">
-        <v>0.594677</v>
+        <v>0.667118</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>1.01967</v>
+        <v>0.849615</v>
       </c>
       <c r="D60" t="n">
-        <v>0.594462</v>
+        <v>0.666964</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>1.015345</v>
+        <v>0.850265</v>
       </c>
       <c r="D61" t="n">
-        <v>0.594711</v>
+        <v>0.66681</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>1.646294</v>
+        <v>0.8526820000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>0.165183</v>
+        <v>0.665914</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>1.496521</v>
+        <v>0.851814</v>
       </c>
       <c r="D63" t="n">
-        <v>0.220711</v>
+        <v>0.665732</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>1.391103</v>
+        <v>0.84948</v>
       </c>
       <c r="D64" t="n">
-        <v>0.23695</v>
+        <v>0.665759</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>1.302979</v>
+        <v>0.846788</v>
       </c>
       <c r="D65" t="n">
-        <v>0.319383</v>
+        <v>0.666225</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>1.225185</v>
+        <v>1.684984</v>
       </c>
       <c r="D66" t="n">
-        <v>0.456973</v>
+        <v>0.167842</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>1.153692</v>
+        <v>1.555532</v>
       </c>
       <c r="D67" t="n">
-        <v>0.496422</v>
+        <v>0.236556</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C68" t="n">
-        <v>1.088346</v>
+        <v>1.48496</v>
       </c>
       <c r="D68" t="n">
-        <v>0.5198660000000001</v>
+        <v>0.295448</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C69" t="n">
-        <v>1.026713</v>
+        <v>1.439392</v>
       </c>
       <c r="D69" t="n">
-        <v>0.530378</v>
+        <v>0.437717</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C70" t="n">
-        <v>0.968283</v>
+        <v>1.407687</v>
       </c>
       <c r="D70" t="n">
-        <v>0.528791</v>
+        <v>0.502595</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C71" t="n">
-        <v>0.914606</v>
+        <v>1.379428</v>
       </c>
       <c r="D71" t="n">
-        <v>0.528142</v>
+        <v>0.5042410000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C72" t="n">
-        <v>0.863941</v>
+        <v>1.34971</v>
       </c>
       <c r="D72" t="n">
-        <v>0.52207</v>
+        <v>0.523212</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C73" t="n">
-        <v>0.816103</v>
+        <v>1.327343</v>
       </c>
       <c r="D73" t="n">
-        <v>0.512099</v>
+        <v>0.553609</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C74" t="n">
-        <v>0.769879</v>
+        <v>1.305463</v>
       </c>
       <c r="D74" t="n">
-        <v>0.5035269999999999</v>
+        <v>0.567991</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C75" t="n">
-        <v>0.725803</v>
+        <v>1.28968</v>
       </c>
       <c r="D75" t="n">
-        <v>0.496363</v>
+        <v>0.598015</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C76" t="n">
-        <v>0.68028</v>
+        <v>1.267175</v>
       </c>
       <c r="D76" t="n">
-        <v>0.496037</v>
+        <v>0.602527</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C77" t="n">
-        <v>0.638662</v>
+        <v>1.252562</v>
       </c>
       <c r="D77" t="n">
-        <v>0.496427</v>
+        <v>0.595769</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C78" t="n">
-        <v>0.634414</v>
+        <v>1.234011</v>
       </c>
       <c r="D78" t="n">
-        <v>0.497552</v>
+        <v>0.59601</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C79" t="n">
-        <v>0.6314920000000001</v>
+        <v>1.220075</v>
       </c>
       <c r="D79" t="n">
-        <v>0.502486</v>
+        <v>0.59297</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C80" t="n">
-        <v>0.62968</v>
+        <v>1.211093</v>
       </c>
       <c r="D80" t="n">
-        <v>0.5050519999999999</v>
+        <v>0.597039</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>0.625827</v>
+        <v>1.192777</v>
       </c>
       <c r="D81" t="n">
-        <v>0.507709</v>
+        <v>0.598992</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C82" t="n">
-        <v>0.623126</v>
+        <v>1.183501</v>
       </c>
       <c r="D82" t="n">
-        <v>0.50863</v>
+        <v>0.603903</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C83" t="n">
-        <v>0.622736</v>
+        <v>1.165359</v>
       </c>
       <c r="D83" t="n">
-        <v>0.509853</v>
+        <v>0.613462</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C84" t="n">
-        <v>0.62071</v>
+        <v>1.160518</v>
       </c>
       <c r="D84" t="n">
-        <v>0.510159</v>
+        <v>0.621739</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C85" t="n">
-        <v>0.619587</v>
+        <v>1.151041</v>
       </c>
       <c r="D85" t="n">
-        <v>0.511012</v>
+        <v>0.618873</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C86" t="n">
-        <v>0.620113</v>
+        <v>1.138445</v>
       </c>
       <c r="D86" t="n">
-        <v>0.511229</v>
+        <v>0.623658</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6192879999999999</v>
+        <v>1.13143</v>
       </c>
       <c r="D87" t="n">
-        <v>0.511244</v>
+        <v>0.631956</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C88" t="n">
-        <v>0.618624</v>
+        <v>1.119819</v>
       </c>
       <c r="D88" t="n">
-        <v>0.511737</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C89" t="n">
-        <v>0.616831</v>
+        <v>1.116281</v>
       </c>
       <c r="D89" t="n">
-        <v>0.511472</v>
+        <v>0.632204</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C90" t="n">
-        <v>0.6171450000000001</v>
+        <v>1.105369</v>
       </c>
       <c r="D90" t="n">
-        <v>0.5120749999999999</v>
+        <v>0.633227</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C91" t="n">
-        <v>0.616686</v>
+        <v>1.099468</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5120980000000001</v>
+        <v>0.6318279999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C92" t="n">
-        <v>1.585089</v>
+        <v>1.089676</v>
       </c>
       <c r="D92" t="n">
-        <v>0.180235</v>
+        <v>0.643865</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C93" t="n">
-        <v>1.418329</v>
+        <v>1.08596</v>
       </c>
       <c r="D93" t="n">
-        <v>0.292267</v>
+        <v>0.642775</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="C94" t="n">
-        <v>1.303824</v>
+        <v>1.07992</v>
       </c>
       <c r="D94" t="n">
-        <v>0.302603</v>
+        <v>0.6392600000000001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C95" t="n">
-        <v>1.207695</v>
+        <v>1.072793</v>
       </c>
       <c r="D95" t="n">
-        <v>0.32788</v>
+        <v>0.6391559999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C96" t="n">
-        <v>1.141688</v>
+        <v>1.06898</v>
       </c>
       <c r="D96" t="n">
-        <v>0.403744</v>
+        <v>0.646123</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C97" t="n">
-        <v>1.072218</v>
+        <v>1.063262</v>
       </c>
       <c r="D97" t="n">
-        <v>0.461051</v>
+        <v>0.653842</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C98" t="n">
-        <v>1.014766</v>
+        <v>1.061374</v>
       </c>
       <c r="D98" t="n">
-        <v>0.492893</v>
+        <v>0.655528</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C99" t="n">
-        <v>0.957622</v>
+        <v>1.055091</v>
       </c>
       <c r="D99" t="n">
-        <v>0.519253</v>
+        <v>0.653292</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C100" t="n">
-        <v>0.902955</v>
+        <v>1.050333</v>
       </c>
       <c r="D100" t="n">
-        <v>0.53516</v>
+        <v>0.658411</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="C101" t="n">
-        <v>0.854877</v>
+        <v>1.051809</v>
       </c>
       <c r="D101" t="n">
-        <v>0.539824</v>
+        <v>0.6561940000000001</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8060619999999999</v>
+        <v>1.042917</v>
       </c>
       <c r="D102" t="n">
-        <v>0.539942</v>
+        <v>0.656945</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="C103" t="n">
-        <v>0.763176</v>
+        <v>1.044643</v>
       </c>
       <c r="D103" t="n">
-        <v>0.539723</v>
+        <v>0.655087</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C104" t="n">
-        <v>0.718224</v>
+        <v>1.036212</v>
       </c>
       <c r="D104" t="n">
-        <v>0.538205</v>
+        <v>0.658403</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C105" t="n">
-        <v>0.677973</v>
+        <v>1.030524</v>
       </c>
       <c r="D105" t="n">
-        <v>0.5358540000000001</v>
+        <v>0.657927</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C106" t="n">
-        <v>0.636479</v>
+        <v>1.035135</v>
       </c>
       <c r="D106" t="n">
-        <v>0.533211</v>
+        <v>0.657061</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C107" t="n">
-        <v>0.596375</v>
+        <v>1.030417</v>
       </c>
       <c r="D107" t="n">
-        <v>0.5300550000000001</v>
+        <v>0.65891</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C108" t="n">
-        <v>0.594602</v>
+        <v>1.026237</v>
       </c>
       <c r="D108" t="n">
-        <v>0.528451</v>
+        <v>0.661612</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C109" t="n">
-        <v>0.5899180000000001</v>
+        <v>1.023341</v>
       </c>
       <c r="D109" t="n">
-        <v>0.529126</v>
+        <v>0.662235</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C110" t="n">
-        <v>0.587777</v>
+        <v>1.01992</v>
       </c>
       <c r="D110" t="n">
-        <v>0.531372</v>
+        <v>0.660987</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C111" t="n">
-        <v>0.5858680000000001</v>
+        <v>1.016848</v>
       </c>
       <c r="D111" t="n">
-        <v>0.532951</v>
+        <v>0.6595760000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C112" t="n">
-        <v>0.583341</v>
+        <v>1.016411</v>
       </c>
       <c r="D112" t="n">
-        <v>0.534458</v>
+        <v>0.659485</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C113" t="n">
-        <v>0.582813</v>
+        <v>1.014292</v>
       </c>
       <c r="D113" t="n">
-        <v>0.53495</v>
+        <v>0.658497</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="C114" t="n">
-        <v>0.5834589999999999</v>
+        <v>1.015529</v>
       </c>
       <c r="D114" t="n">
-        <v>0.536083</v>
+        <v>0.660006</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C115" t="n">
-        <v>0.582094</v>
+        <v>1.011286</v>
       </c>
       <c r="D115" t="n">
-        <v>0.5382439999999999</v>
+        <v>0.660679</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="C116" t="n">
-        <v>0.578921</v>
+        <v>1.010669</v>
       </c>
       <c r="D116" t="n">
-        <v>0.540447</v>
+        <v>0.661628</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="C117" t="n">
-        <v>0.581519</v>
+        <v>1.007178</v>
       </c>
       <c r="D117" t="n">
-        <v>0.540978</v>
+        <v>0.660308</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="C118" t="n">
-        <v>0.58041</v>
+        <v>1.009218</v>
       </c>
       <c r="D118" t="n">
-        <v>0.53998</v>
+        <v>0.660756</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C119" t="n">
-        <v>0.579705</v>
+        <v>1.007481</v>
       </c>
       <c r="D119" t="n">
-        <v>0.539804</v>
+        <v>0.658878</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="C120" t="n">
-        <v>0.580789</v>
+        <v>1.007906</v>
       </c>
       <c r="D120" t="n">
-        <v>0.539655</v>
+        <v>0.658836</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C121" t="n">
-        <v>0.5792580000000001</v>
+        <v>1.004434</v>
       </c>
       <c r="D121" t="n">
-        <v>0.539426</v>
+        <v>0.659926</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="C122" t="n">
-        <v>1.367657</v>
+        <v>1.0056</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
+        <v>0.660178</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="C123" t="n">
-        <v>1.161079</v>
+        <v>1.002493</v>
       </c>
       <c r="D123" t="n">
-        <v>0.00144</v>
+        <v>0.659976</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>PLWCE+Dice                  (α=7.763) [baseline]</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="C124" t="n">
-        <v>1.047755</v>
+        <v>1.004636</v>
       </c>
       <c r="D124" t="n">
-        <v>0.032603</v>
+        <v>0.66025</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>0.956058</v>
+        <v>1.531025</v>
       </c>
       <c r="D125" t="n">
-        <v>0.148863</v>
+        <v>0.164827</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C126" t="n">
-        <v>0.885015</v>
+        <v>1.378084</v>
       </c>
       <c r="D126" t="n">
-        <v>0.298974</v>
+        <v>0.230388</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C127" t="n">
-        <v>0.825001</v>
+        <v>1.319373</v>
       </c>
       <c r="D127" t="n">
-        <v>0.439274</v>
+        <v>0.510834</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C128" t="n">
-        <v>0.7683990000000001</v>
+        <v>1.279678</v>
       </c>
       <c r="D128" t="n">
-        <v>0.524773</v>
+        <v>0.45297</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C129" t="n">
-        <v>0.721882</v>
+        <v>1.247682</v>
       </c>
       <c r="D129" t="n">
-        <v>0.571229</v>
+        <v>0.437318</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C130" t="n">
-        <v>0.677623</v>
+        <v>1.221828</v>
       </c>
       <c r="D130" t="n">
-        <v>0.607328</v>
+        <v>0.472517</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C131" t="n">
-        <v>0.638786</v>
+        <v>1.195983</v>
       </c>
       <c r="D131" t="n">
-        <v>0.623711</v>
+        <v>0.517245</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C132" t="n">
-        <v>0.599979</v>
+        <v>1.173483</v>
       </c>
       <c r="D132" t="n">
-        <v>0.627968</v>
+        <v>0.559239</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C133" t="n">
-        <v>0.565361</v>
+        <v>1.154789</v>
       </c>
       <c r="D133" t="n">
-        <v>0.634426</v>
+        <v>0.59254</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C134" t="n">
-        <v>0.530451</v>
+        <v>1.134164</v>
       </c>
       <c r="D134" t="n">
-        <v>0.637167</v>
+        <v>0.606566</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C135" t="n">
-        <v>0.498591</v>
+        <v>1.117334</v>
       </c>
       <c r="D135" t="n">
-        <v>0.639819</v>
+        <v>0.612896</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C136" t="n">
-        <v>0.467665</v>
+        <v>1.102895</v>
       </c>
       <c r="D136" t="n">
-        <v>0.642077</v>
+        <v>0.615959</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C137" t="n">
-        <v>0.438916</v>
+        <v>1.090345</v>
       </c>
       <c r="D137" t="n">
-        <v>0.643899</v>
+        <v>0.617953</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C138" t="n">
-        <v>0.43445</v>
+        <v>1.075718</v>
       </c>
       <c r="D138" t="n">
-        <v>0.643855</v>
+        <v>0.616873</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C139" t="n">
-        <v>0.431806</v>
+        <v>1.063569</v>
       </c>
       <c r="D139" t="n">
-        <v>0.643743</v>
+        <v>0.618708</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>0.42961</v>
+        <v>1.049628</v>
       </c>
       <c r="D140" t="n">
-        <v>0.643739</v>
+        <v>0.621379</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C141" t="n">
-        <v>0.428332</v>
+        <v>1.032381</v>
       </c>
       <c r="D141" t="n">
-        <v>0.642976</v>
+        <v>0.623287</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C142" t="n">
-        <v>0.425313</v>
+        <v>1.017043</v>
       </c>
       <c r="D142" t="n">
-        <v>0.64374</v>
+        <v>0.627818</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C143" t="n">
-        <v>0.42406</v>
+        <v>1.001354</v>
       </c>
       <c r="D143" t="n">
-        <v>0.644993</v>
+        <v>0.636099</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C144" t="n">
-        <v>0.42341</v>
+        <v>0.987101</v>
       </c>
       <c r="D144" t="n">
-        <v>0.646734</v>
+        <v>0.6421559999999999</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C145" t="n">
-        <v>0.422074</v>
+        <v>0.972857</v>
       </c>
       <c r="D145" t="n">
-        <v>0.646862</v>
+        <v>0.647334</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C146" t="n">
-        <v>0.420291</v>
+        <v>0.961245</v>
       </c>
       <c r="D146" t="n">
-        <v>0.646872</v>
+        <v>0.649762</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C147" t="n">
-        <v>0.421836</v>
+        <v>0.948406</v>
       </c>
       <c r="D147" t="n">
-        <v>0.646892</v>
+        <v>0.649398</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C148" t="n">
-        <v>0.419655</v>
+        <v>0.936169</v>
       </c>
       <c r="D148" t="n">
-        <v>0.646388</v>
+        <v>0.65221</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C149" t="n">
-        <v>0.419747</v>
+        <v>0.922633</v>
       </c>
       <c r="D149" t="n">
-        <v>0.64654</v>
+        <v>0.652535</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C150" t="n">
-        <v>0.419557</v>
+        <v>0.911342</v>
       </c>
       <c r="D150" t="n">
-        <v>0.646597</v>
+        <v>0.651775</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+          <t>CE+Dice+BL                  [literature]</t>
         </is>
       </c>
       <c r="B151" t="n">
+        <v>27</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.899617</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.654238</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>28</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.887966</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.657509</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>29</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.8787779999999999</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.660373</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
         <v>30</v>
       </c>
-      <c r="C151" t="n">
-        <v>0.419042</v>
-      </c>
-      <c r="D151" t="n">
-        <v>0.646732</v>
+      <c r="C154" t="n">
+        <v>0.871537</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.664456</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>31</v>
+      </c>
+      <c r="C155" t="n">
+        <v>0.859627</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.667629</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>32</v>
+      </c>
+      <c r="C156" t="n">
+        <v>0.8504350000000001</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.668297</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>33</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.84518</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.668088</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>34</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.8330920000000001</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.667937</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>35</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.82886</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.667018</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>36</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.8193780000000001</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.665551</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>37</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.812756</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.662297</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>38</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.799708</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.658765</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>39</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.795812</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.657025</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>40</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.789365</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.658429</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>41</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.78144</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.659332</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>42</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.771869</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.659615</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>43</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.7685110000000001</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.659456</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>44</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.759001</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.659047</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>45</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.752734</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.660215</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>46</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.747429</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.662211</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>47</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.740362</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.664552</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="n">
+        <v>1.469547</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.166839</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2</v>
+      </c>
+      <c r="C173" t="n">
+        <v>1.362905</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.334697</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>3</v>
+      </c>
+      <c r="C174" t="n">
+        <v>1.307421</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.295923</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>4</v>
+      </c>
+      <c r="C175" t="n">
+        <v>1.269769</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.286998</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>5</v>
+      </c>
+      <c r="C176" t="n">
+        <v>1.236384</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.376524</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>6</v>
+      </c>
+      <c r="C177" t="n">
+        <v>1.206232</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.472799</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>7</v>
+      </c>
+      <c r="C178" t="n">
+        <v>1.183965</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.5389119999999999</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>8</v>
+      </c>
+      <c r="C179" t="n">
+        <v>1.163774</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.577666</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>9</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1.143121</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.596576</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>10</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1.12885</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.605672</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>11</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1.110068</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.6100179999999999</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>12</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1.09525</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.619306</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>13</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1.083277</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.622862</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>14</v>
+      </c>
+      <c r="C185" t="n">
+        <v>1.073558</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.628807</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>15</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1.05722</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.633495</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>1.053435</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.635184</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>17</v>
+      </c>
+      <c r="C188" t="n">
+        <v>1.028883</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.636243</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>18</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1.018446</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.6409550000000001</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>19</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1.004236</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.641662</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>20</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.990072</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.642083</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>21</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.97504</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.646765</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>22</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.96774</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.6499549999999999</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>23</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.953606</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.652379</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>24</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.942659</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.651288</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>25</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.936866</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.651494</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>26</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.921064</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.654132</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>27</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.909988</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.658121</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>28</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.902937</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.656372</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>29</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.893371</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.653331</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>30</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.883181</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.651243</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>31</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.881064</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.653931</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>32</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.868801</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.65885</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>33</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.862104</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.658513</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>34</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.851305</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.6588079999999999</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>35</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.843857</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.660815</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>36</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.836207</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.661243</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>37</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.827785</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.658667</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>38</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.820302</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.656576</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>39</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.812002</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.660185</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>40</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.808244</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.661754</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>41</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.7990390000000001</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.6602209999999999</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>42</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.7954870000000001</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.6576880000000001</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>43</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.785365</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.656824</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>44</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.7807500000000001</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.656235</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>45</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.773656</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.658047</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>46</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.7679859999999999</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.658124</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>47</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.760656</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.6575260000000001</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>48</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.753317</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.657407</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>49</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.749001</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.657977</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>50</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.744714</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.658134</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>51</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.735432</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.657726</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>52</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.730457</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.656434</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>53</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.725982</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.655334</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>54</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.722931</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.656444</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>55</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.71417</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.657988</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" t="n">
+        <v>1.448135</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.164835</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>2</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1.283184</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.176992</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>3</v>
+      </c>
+      <c r="C229" t="n">
+        <v>1.198289</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.198683</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>4</v>
+      </c>
+      <c r="C230" t="n">
+        <v>1.141478</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.360146</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>5</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1.083113</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.403121</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>6</v>
+      </c>
+      <c r="C232" t="n">
+        <v>1.040105</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.461987</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>7</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1.003691</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.499519</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>8</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.973321</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.550771</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>9</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.942407</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.569693</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>10</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.924589</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.572661</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>11</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.896424</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.577437</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>12</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.876904</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.582163</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>13</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.864848</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.597846</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>14</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.8488869999999999</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.6040219999999999</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>15</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.831713</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.6091490000000001</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>16</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.819731</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.612842</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>17</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.80241</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.623967</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>18</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.78363</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.633567</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>19</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.768122</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.631872</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>20</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.753058</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.635675</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>21</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.742781</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.637522</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>22</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.722491</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.642728</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>23</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.710572</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.643556</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>24</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.700044</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.6475109999999999</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>25</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.688863</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.649676</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>26</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.67623</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.647746</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>27</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.665893</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.651321</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>28</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.653089</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.6563099999999999</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>29</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.643966</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.653486</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>30</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.634061</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.653857</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>31</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.625047</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.657008</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>32</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.619069</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.661124</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>33</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.6085739999999999</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.663649</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>34</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.600136</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.666391</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>35</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.591661</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.666571</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>36</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.583866</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.666094</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>37</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.572828</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.667544</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>38</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.566381</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.6681280000000001</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>39</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.558894</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.669073</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>40</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.5510620000000001</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.67037</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>41</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.547315</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.670341</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>42</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.541145</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.669492</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>43</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.533442</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.6686530000000001</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>44</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.526648</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.669448</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>45</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.519455</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.669759</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>46</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.5148239999999999</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.668716</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>47</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.507836</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.667728</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>48</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.500049</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.667299</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>49</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.494052</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.666703</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>50</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.487438</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.667187</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>51</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.481546</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.667283</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>52</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.667317</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>53</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.470757</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.668234</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>54</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.463357</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.668588</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=7.763)</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>55</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.459663</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.668009</v>
       </c>
     </row>
   </sheetData>
